--- a/data/UV-Vis/2_CdS_JOliveira_21abr26.xlsx
+++ b/data/UV-Vis/2_CdS_JOliveira_21abr26.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="18" documentId="8_{A565BBC2-F545-4564-B03D-71A98F3E0A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4144A370-291F-4C68-94F6-FE26D7B41C4A}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CdS1" sheetId="1" r:id="rId1"/>
@@ -28181,6 +28181,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
